--- a/research/traditional_assets/database/data/india/india_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/india/india_reinsurance.xlsx
@@ -588,73 +588,76 @@
         </is>
       </c>
       <c r="F2">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="G2">
-        <v>0.07391412030587288</v>
+        <v>0.07401934674661947</v>
       </c>
       <c r="H2">
-        <v>0.07391412030587288</v>
+        <v>0.07401934674661947</v>
       </c>
       <c r="I2">
-        <v>0.07162316956131388</v>
+        <v>0.1296541296541296</v>
       </c>
       <c r="J2">
-        <v>0.04995589852786103</v>
+        <v>0.08457729497568871</v>
       </c>
       <c r="K2">
-        <v>346.3</v>
+        <v>617.4</v>
       </c>
       <c r="L2">
-        <v>0.05360515154329588</v>
+        <v>0.106080651535197</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.01279953552200992</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.07855523161645611</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.01279953552200992</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.07855523161645611</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>2591.9</v>
+        <v>2813.9</v>
       </c>
       <c r="V2">
-        <v>0.7831933280957273</v>
+        <v>0.7426105774305922</v>
       </c>
       <c r="W2">
-        <v>0.05885952239313334</v>
+        <v>0.07754333082140165</v>
       </c>
       <c r="X2">
-        <v>0.1041180051972358</v>
+        <v>0.1449800724341496</v>
       </c>
       <c r="Y2">
-        <v>-0.04525848280410247</v>
+        <v>-0.06743674161274797</v>
       </c>
       <c r="Z2">
-        <v>1.822043220009138</v>
+        <v>1.084542552656245</v>
       </c>
       <c r="AA2">
-        <v>0.09102180621215367</v>
+        <v>0.09172767538969363</v>
       </c>
       <c r="AB2">
-        <v>0.1041180051972358</v>
+        <v>0.1449800724341496</v>
       </c>
       <c r="AC2">
-        <v>-0.01309619898508214</v>
+        <v>-0.05325239704445599</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -666,7 +669,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-2591.9</v>
+        <v>-2813.9</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -675,22 +678,28 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-3.612404181184669</v>
+        <v>-2.885163539423768</v>
       </c>
       <c r="AK2">
-        <v>-0.4826539543025269</v>
+        <v>-0.5607836103471642</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>7.71</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>7.71</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
+      <c r="AO2">
+        <v>97.87289234760053</v>
+      </c>
       <c r="AP2">
-        <v>-5.579978471474704</v>
+        <v>-3.725046333068573</v>
+      </c>
+      <c r="AQ2">
+        <v>97.87289234760053</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>General Insurance Corporation of India (BSE:540755)</t>
+          <t>General Insurance Corporation of India (NSEI:GICRE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,73 +719,76 @@
         </is>
       </c>
       <c r="F3">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="G3">
-        <v>0.07391412030587288</v>
+        <v>0.07401934674661947</v>
       </c>
       <c r="H3">
-        <v>0.07391412030587288</v>
+        <v>0.07401934674661947</v>
       </c>
       <c r="I3">
-        <v>0.07162316956131388</v>
+        <v>0.1296541296541296</v>
       </c>
       <c r="J3">
-        <v>0.04995589852786103</v>
+        <v>0.08457729497568871</v>
       </c>
       <c r="K3">
-        <v>346.3</v>
+        <v>617.4</v>
       </c>
       <c r="L3">
-        <v>0.05360515154329588</v>
+        <v>0.106080651535197</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>48.5</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.01279953552200992</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.07855523161645611</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>48.5</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.01279953552200992</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.07855523161645611</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>2591.9</v>
+        <v>2813.9</v>
       </c>
       <c r="V3">
-        <v>0.7831933280957273</v>
+        <v>0.7426105774305922</v>
       </c>
       <c r="W3">
-        <v>0.05885952239313334</v>
+        <v>0.07754333082140165</v>
       </c>
       <c r="X3">
-        <v>0.1041180051972358</v>
+        <v>0.1449800724341496</v>
       </c>
       <c r="Y3">
-        <v>-0.04525848280410247</v>
+        <v>-0.06743674161274797</v>
       </c>
       <c r="Z3">
-        <v>1.822043220009138</v>
+        <v>1.084542552656245</v>
       </c>
       <c r="AA3">
-        <v>0.09102180621215367</v>
+        <v>0.09172767538969363</v>
       </c>
       <c r="AB3">
-        <v>0.1041180051972358</v>
+        <v>0.1449800724341496</v>
       </c>
       <c r="AC3">
-        <v>-0.01309619898508214</v>
+        <v>-0.05325239704445599</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -788,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-2591.9</v>
+        <v>-2813.9</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -797,22 +809,28 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-3.612404181184669</v>
+        <v>-2.885163539423768</v>
       </c>
       <c r="AK3">
-        <v>-0.4826539543025269</v>
+        <v>-0.5607836103471642</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>7.71</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>7.71</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
+      <c r="AO3">
+        <v>97.87289234760053</v>
+      </c>
       <c r="AP3">
-        <v>-5.579978471474704</v>
+        <v>-3.725046333068573</v>
+      </c>
+      <c r="AQ3">
+        <v>97.87289234760053</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/india/india_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/india/india_reinsurance.xlsx
@@ -588,43 +588,43 @@
         </is>
       </c>
       <c r="F2">
-        <v>0.11</v>
+        <v>-0.052</v>
       </c>
       <c r="G2">
-        <v>0.07401934674661947</v>
+        <v>0.1580068604441235</v>
       </c>
       <c r="H2">
-        <v>0.07401934674661947</v>
+        <v>0.1580068604441235</v>
       </c>
       <c r="I2">
-        <v>0.1296541296541296</v>
+        <v>0.1501715111030872</v>
       </c>
       <c r="J2">
-        <v>0.08457729497568871</v>
+        <v>0.1309936929346632</v>
       </c>
       <c r="K2">
-        <v>617.4</v>
+        <v>797.8</v>
       </c>
       <c r="L2">
-        <v>0.106080651535197</v>
+        <v>0.1440332189925979</v>
       </c>
       <c r="M2">
-        <v>48.5</v>
+        <v>152</v>
       </c>
       <c r="N2">
-        <v>0.01279953552200992</v>
+        <v>0.02311751912518441</v>
       </c>
       <c r="O2">
-        <v>0.07855523161645611</v>
+        <v>0.1905239408373026</v>
       </c>
       <c r="P2">
-        <v>48.5</v>
+        <v>152</v>
       </c>
       <c r="Q2">
-        <v>0.01279953552200992</v>
+        <v>0.02311751912518441</v>
       </c>
       <c r="R2">
-        <v>0.07855523161645611</v>
+        <v>0.1905239408373026</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,31 +633,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2813.9</v>
+        <v>2851.6</v>
       </c>
       <c r="V2">
-        <v>0.7426105774305922</v>
+        <v>0.4336968259037885</v>
       </c>
       <c r="W2">
-        <v>0.07754333082140165</v>
+        <v>0.1018680490825747</v>
       </c>
       <c r="X2">
-        <v>0.1449800724341496</v>
+        <v>0.1224542592446282</v>
       </c>
       <c r="Y2">
-        <v>-0.06743674161274797</v>
+        <v>-0.02058621016205354</v>
       </c>
       <c r="Z2">
-        <v>1.084542552656245</v>
+        <v>1.104609886647363</v>
       </c>
       <c r="AA2">
-        <v>0.09172767538969363</v>
+        <v>0.1446969283040777</v>
       </c>
       <c r="AB2">
-        <v>0.1449800724341496</v>
+        <v>0.1224542592446282</v>
       </c>
       <c r="AC2">
-        <v>-0.05325239704445599</v>
+        <v>0.02224266905944954</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -669,7 +669,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-2813.9</v>
+        <v>-2851.6</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -678,28 +678,28 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-2.885163539423768</v>
+        <v>-0.7658385927219014</v>
       </c>
       <c r="AK2">
-        <v>-0.5607836103471642</v>
+        <v>-0.4611105721031015</v>
       </c>
       <c r="AL2">
-        <v>7.71</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="AM2">
-        <v>7.71</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AO2">
-        <v>97.87289234760053</v>
+        <v>85.57613168724279</v>
       </c>
       <c r="AP2">
-        <v>-3.725046333068573</v>
+        <v>-3.424111431316042</v>
       </c>
       <c r="AQ2">
-        <v>97.87289234760053</v>
+        <v>85.57613168724279</v>
       </c>
     </row>
     <row r="3">
@@ -719,43 +719,43 @@
         </is>
       </c>
       <c r="F3">
-        <v>0.11</v>
+        <v>-0.052</v>
       </c>
       <c r="G3">
-        <v>0.07401934674661947</v>
+        <v>0.1580068604441235</v>
       </c>
       <c r="H3">
-        <v>0.07401934674661947</v>
+        <v>0.1580068604441235</v>
       </c>
       <c r="I3">
-        <v>0.1296541296541296</v>
+        <v>0.1501715111030872</v>
       </c>
       <c r="J3">
-        <v>0.08457729497568871</v>
+        <v>0.1309936929346632</v>
       </c>
       <c r="K3">
-        <v>617.4</v>
+        <v>797.8</v>
       </c>
       <c r="L3">
-        <v>0.106080651535197</v>
+        <v>0.1440332189925979</v>
       </c>
       <c r="M3">
-        <v>48.5</v>
+        <v>152</v>
       </c>
       <c r="N3">
-        <v>0.01279953552200992</v>
+        <v>0.02311751912518441</v>
       </c>
       <c r="O3">
-        <v>0.07855523161645611</v>
+        <v>0.1905239408373026</v>
       </c>
       <c r="P3">
-        <v>48.5</v>
+        <v>152</v>
       </c>
       <c r="Q3">
-        <v>0.01279953552200992</v>
+        <v>0.02311751912518441</v>
       </c>
       <c r="R3">
-        <v>0.07855523161645611</v>
+        <v>0.1905239408373026</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,31 +764,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2813.9</v>
+        <v>2851.6</v>
       </c>
       <c r="V3">
-        <v>0.7426105774305922</v>
+        <v>0.4336968259037885</v>
       </c>
       <c r="W3">
-        <v>0.07754333082140165</v>
+        <v>0.1018680490825747</v>
       </c>
       <c r="X3">
-        <v>0.1449800724341496</v>
+        <v>0.1224542592446282</v>
       </c>
       <c r="Y3">
-        <v>-0.06743674161274797</v>
+        <v>-0.02058621016205354</v>
       </c>
       <c r="Z3">
-        <v>1.084542552656245</v>
+        <v>1.104609886647363</v>
       </c>
       <c r="AA3">
-        <v>0.09172767538969363</v>
+        <v>0.1446969283040777</v>
       </c>
       <c r="AB3">
-        <v>0.1449800724341496</v>
+        <v>0.1224542592446282</v>
       </c>
       <c r="AC3">
-        <v>-0.05325239704445599</v>
+        <v>0.02224266905944954</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-2813.9</v>
+        <v>-2851.6</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -809,28 +809,28 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-2.885163539423768</v>
+        <v>-0.7658385927219014</v>
       </c>
       <c r="AK3">
-        <v>-0.5607836103471642</v>
+        <v>-0.4611105721031015</v>
       </c>
       <c r="AL3">
-        <v>7.71</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="AM3">
-        <v>7.71</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>97.87289234760053</v>
+        <v>85.57613168724279</v>
       </c>
       <c r="AP3">
-        <v>-3.725046333068573</v>
+        <v>-3.424111431316042</v>
       </c>
       <c r="AQ3">
-        <v>97.87289234760053</v>
+        <v>85.57613168724279</v>
       </c>
     </row>
   </sheetData>
